--- a/data/v5_4_hk.xlsx
+++ b/data/v5_4_hk.xlsx
@@ -3511,12 +3511,12 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>0688.HK</t>
+          <t>1908.HK</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>中国海外发展</t>
+          <t>建发国际集团</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -3534,18 +3534,18 @@
         <v>4</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>13.17</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>1908.HK</t>
+          <t>0688.HK</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>建发国际集团</t>
+          <t>中国海外发展</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -3563,7 +3563,7 @@
         <v>4</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>12.8</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="36">
@@ -3712,72 +3712,72 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>9999.HK</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>网易-S</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr"/>
+      <c r="F41" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>9618.HK</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>京东集团-SW</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>B·EXIT 🔴</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="n">
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>106.9</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>9888.HK</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>百度集团-SW</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr"/>
-      <c r="F42" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>91.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>9888.HK</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>网易-S</t>
+          <t>百度集团-SW</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -3795,7 +3795,7 @@
         <v>3</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>183</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="44">

--- a/data/v5_4_hk.xlsx
+++ b/data/v5_4_hk.xlsx
@@ -3511,12 +3511,12 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>1908.HK</t>
+          <t>0688.HK</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>建发国际集团</t>
+          <t>中国海外发展</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -3534,18 +3534,18 @@
         <v>4</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>12.8</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>0688.HK</t>
+          <t>0817.HK</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>中国海外发展</t>
+          <t>中国金茂</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -3563,18 +3563,18 @@
         <v>4</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>13.17</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>0817.HK</t>
+          <t>1908.HK</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>中国金茂</t>
+          <t>建发国际集团</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -3592,7 +3592,7 @@
         <v>4</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>1.35</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="37">

--- a/data/v5_4_hk.xlsx
+++ b/data/v5_4_hk.xlsx
@@ -10184,7 +10184,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>扫描日期：2026-09-06</t>
+          <t>扫描日期：2026-09-07</t>
         </is>
       </c>
     </row>

--- a/data/v5_4_hk.xlsx
+++ b/data/v5_4_hk.xlsx
@@ -79,12 +79,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECEFF1"/>
-        <bgColor rgb="00ECEFF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E3F2FD"/>
         <bgColor rgb="00E3F2FD"/>
       </patternFill>
@@ -111,6 +105,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FBE9E7"/>
         <bgColor rgb="00FBE9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECEFF1"/>
+        <bgColor rgb="00ECEFF1"/>
       </patternFill>
     </fill>
   </fills>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>13.3</v>
+        <v>13.53</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>12.628</v>
+        <v>12.651</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5.24</v>
+        <v>5.43</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-1.68</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="3">
@@ -664,16 +664,16 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>8.57</v>
+        <v>8.82</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8.337</v>
+        <v>8.363</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3.31</v>
+        <v>3.62</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-4.03</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="4">
@@ -708,720 +708,940 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>4.055</v>
+        <v>4.05</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6.08</v>
+        <v>5.95</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-1.58</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>2015.HK</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>理想汽车-W</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>SOS-B</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
           <t>2525.HK</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>禾赛-W</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>智能驾驶</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>SOS-B</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G6" s="3" t="n">
         <v>18.53</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>17.205</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I6" s="3" t="n">
         <v>-5.85</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>-2.17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>9926.HK</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>康方生物</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>创新药</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>SETUP_OK</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>SOS-B</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>-1.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>9926.HK</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>康方生物</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>SOS-B</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>2196.HK</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>复星医药</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>药品及生物科技</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>SOS-B</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>-3.62</v>
-      </c>
-      <c r="J7" s="4" t="n">
+      <c r="G8" s="4" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>16.431</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>-3.68</v>
+      </c>
+      <c r="J8" s="4" t="n">
         <v>-3.13</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>0285.HK</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪电子</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>消费电子</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>SOS-B</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>25.092</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>-4.22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>1729.HK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>汇聚科技</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>资讯科技器材</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>SOS-B</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>16.885</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2400.HK</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>心动公司</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>软件服务</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>SOS-B</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>45.06</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>41.744</v>
-      </c>
-      <c r="I8" s="5" t="n">
+      <c r="G11" s="5" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>41.742</v>
+      </c>
+      <c r="I11" s="5" t="n">
         <v>-1.76</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J11" s="5" t="n">
         <v>-4.37</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>1988.HK</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>民生银行</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>银行</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>SOS-B</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>3.555</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>3.495</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="J9" s="6" t="n">
+      <c r="G12" s="6" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3.494</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>-1.69</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>2202.HK</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>万科企业</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>中国地产&amp;物管</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>0806.HK</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>惠理集团</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>其他金融</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>SOS-B</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>2.425</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>-6.36</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="G13" s="6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.999</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>0136.HK</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>中国儒意</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>媒体及娱乐</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>SOS-B</t>
         </is>
       </c>
-      <c r="G11" s="8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>1.366</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>-4.17</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>-6.68</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="G14" s="7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>1.372</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>-6.66</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>9626.HK</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>哔哩哔哩-W</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>SOS-B</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>-4.86</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>1138.HK</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>中远海能</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>交运</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>SOS-B</t>
         </is>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>17.49</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>16.707</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="G16" s="8" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>16.691</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>2883.HK</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>中海油田服务</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>能源</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>SOS-B</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J13" s="9" t="n">
+      <c r="G17" s="8" t="n">
+        <v>7.175</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>7.334</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J17" s="8" t="n">
         <v>0.26</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>6198.HK</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>青岛港</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>工用运输</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>7.142</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J14" s="2" t="n">
+      <c r="G18" s="2" t="n">
+        <v>7.345</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>7.144</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>0.06</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>6078.HK</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>海吉亚医疗</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>其他医疗保健</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>10.238</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G19" s="4" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>10.227</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>0354.HK</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>中国软件国际</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>软件服务</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>3.885</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="G20" s="5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>3.892</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>-4.79</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>2799.HK</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>中信金融资产</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>其他金融</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="J17" s="6" t="n">
+      <c r="G21" s="6" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="J21" s="6" t="n">
         <v>-5.06</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>3958.HK</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>东方证券</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>其他金融</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>5.843</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="G22" s="6" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>5.837</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>1797.HK</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>东方甄选</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>零售</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G19" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>25.306</v>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>20.16</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="G23" s="9" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>25.274</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>1357.HK</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>美图公司</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>媒体及娱乐</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G20" s="8" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>4.665</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="J20" s="8" t="n">
+      <c r="G24" s="7" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>4.666</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="J24" s="7" t="n">
         <v>-6.61</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>3668.HK</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>兖煤澳大利亚</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>能源</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>SOS-C</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>33.904</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>
@@ -1435,7 +1655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1546,16 +1766,16 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>56</v>
+        <v>53.55</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>57.49</v>
+        <v>57.245</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>11.94</v>
+        <v>11.46</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>46.525</v>
+        <v>46.484</v>
       </c>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n">
@@ -1594,16 +1814,16 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>48.12</v>
+        <v>47.66</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>46.42</v>
+        <v>46.374</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6.45</v>
+        <v>6.35</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>42.972</v>
+        <v>42.964</v>
       </c>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n">
@@ -1642,16 +1862,16 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>87.65000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>85.94</v>
+        <v>85.61499999999999</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>20.15</v>
+        <v>19.69</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>79.075</v>
+        <v>79.021</v>
       </c>
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n">
@@ -1690,16 +1910,16 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>21.5</v>
+        <v>23.1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>20.205</v>
+        <v>20.365</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>12.66</v>
+        <v>13.55</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>18.352</v>
+        <v>18.379</v>
       </c>
       <c r="K5" s="5" t="n"/>
       <c r="L5" s="5" t="n">
@@ -1709,12 +1929,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>6613.HK</t>
+          <t>6166.HK</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>蓝思科技</t>
+          <t>剑桥科技</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1724,7 +1944,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>AI算力</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1738,33 +1958,31 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>24.34</v>
+        <v>120.2</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>24.304</v>
+        <v>100.695</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>7.34</v>
+        <v>7.87</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>23.596</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>-0.97</v>
-      </c>
+        <v>103.451</v>
+      </c>
+      <c r="K6" s="5" t="n"/>
       <c r="L6" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>6166.HK</t>
+          <t>6613.HK</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>剑桥科技</t>
+          <t>蓝思科技</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1774,7 +1992,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AI算力</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1788,31 +2006,33 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>113.1</v>
+        <v>24.34</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>99.985</v>
+        <v>24.304</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>7.11</v>
+        <v>7.34</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>103.332</v>
-      </c>
-      <c r="K7" s="5" t="n"/>
+        <v>23.596</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>-0.97</v>
+      </c>
       <c r="L7" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>6687.HK</t>
+          <t>3296.HK</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>聚水潭</t>
+          <t>华勤技术</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1822,7 +2042,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>软件服务</t>
+          <t>AI算力</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1836,31 +2056,31 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>13.98</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>14.736</v>
+        <v>76.19499999999999</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>5.09</v>
+        <v>3.43</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>13.898</v>
+        <v>70.488</v>
       </c>
       <c r="K8" s="5" t="n"/>
       <c r="L8" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>9678.HK</t>
+          <t>0100.HK</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云知声</t>
+          <t>MINIMAX-WP</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1870,7 +2090,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>软件服务</t>
+          <t>大模型及其应用</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1884,237 +2104,237 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>88.15000000000001</v>
+        <v>350.8</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>76.02</v>
+        <v>331.32</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>4.31</v>
+        <v>0.22</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>86.223</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>-14.38</v>
-      </c>
+        <v>322.838</v>
+      </c>
+      <c r="K9" s="5" t="n"/>
       <c r="L9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>3296.HK</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>华勤技术</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>AI算力</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>1828.HK</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>富卫集团</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>STRONG NEW</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>76.035</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>70.462</v>
-      </c>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n">
-        <v>10</v>
+      <c r="G10" s="6" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>29.823</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>0100.HK</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>MINIMAX-WP</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>大模型及其应用</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>3887.HK</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>HASHKEY HLDGS</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>其他金融</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>STRONG NEW</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>376.6</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>333.9</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>323.268</v>
-      </c>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n">
-        <v>1</v>
+      <c r="G11" s="6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>1828.HK</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>富卫集团</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>2714.HK</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>牧原股份</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>STRONG NEW</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>32.228</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>29.829</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>7</v>
+      <c r="G12" s="9" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>35.958</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>32.904</v>
+      </c>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>3887.HK</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>HASHKEY HLDGS</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>其他金融</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2259.HK</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>紫金黄金国际</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>贵金属</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>STRONG NEW</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n">
-        <v>2.785</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>2.721</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n">
-        <v>4</v>
+      <c r="G13" s="10" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>156.789</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>121.663</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>2714.HK</t>
+          <t>2788.HK</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>牧原股份</t>
+          <t>创新实业</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -2128,117 +2348,19 @@
         </is>
       </c>
       <c r="G14" s="10" t="n">
-        <v>39.5</v>
+        <v>17.08</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>35.92</v>
+        <v>17.246</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>5.07</v>
+        <v>2.06</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>32.898</v>
+        <v>16.463</v>
       </c>
       <c r="K14" s="10" t="n"/>
       <c r="L14" s="10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>2259.HK</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>紫金黄金国际</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>贵金属</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>STRONG NEW</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>161.9</v>
-      </c>
-      <c r="H15" s="11" t="n">
-        <v>157.009</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>121.699</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>2788.HK</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>创新实业</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>工业金属</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>STRONG NEW</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>17.261</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>16.465</v>
-      </c>
-      <c r="K16" s="11" t="n"/>
-      <c r="L16" s="11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2253,7 +2375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2324,13 +2446,13 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-26.98</v>
+        <v>-29.21</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.475</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="3">
@@ -2355,13 +2477,13 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-18.78</v>
+        <v>-20.12</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>28.98</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="4">
@@ -2386,24 +2508,24 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-18.41</v>
+        <v>-19.08</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>31.82</v>
+        <v>31.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>6127.HK</t>
+          <t>9887.HK</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
+          <t>维立志博-B</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -2417,24 +2539,24 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-17.6</v>
+        <v>-18.27</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>22.66</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>9887.HK</t>
+          <t>6127.HK</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>维立志博-B</t>
+          <t>昭衍新药</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2448,13 +2570,13 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-17.08</v>
+        <v>-18.04</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>63.1</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="7">
@@ -2479,24 +2601,24 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-15.26</v>
+        <v>-15.21</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>149.9</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>1913.HK</t>
+          <t>0116.HK</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>普拉达</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2510,55 +2632,55 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-13.36</v>
+        <v>-13.67</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>39.42</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>0116.HK</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>周生生</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2142.HK</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>和铂医药-B</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>-13.25</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>14.4</v>
+      <c r="E9" s="4" t="n">
+        <v>-12.45</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>14.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>1929.HK</t>
+          <t>1913.HK</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>普拉达</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2572,168 +2694,168 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-12.12</v>
+        <v>-12.18</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.96</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>1929.HK</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-12.05</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>1768.HK</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>鸣鸣很忙</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E12" s="9" t="n">
         <v>-12.05</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G12" s="9" t="n">
         <v>391.2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>6969.HK</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>思摩尔国际</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E12" s="10" t="n">
-        <v>-11.75</v>
-      </c>
-      <c r="F12" s="10" t="n">
+      <c r="E13" s="9" t="n">
+        <v>-11.88</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <v>9.855</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="G13" s="9" t="n">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>0358.HK</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>江西铜业股份</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>-11.64</v>
-      </c>
-      <c r="F13" s="11" t="n">
+      <c r="E14" s="10" t="n">
+        <v>-10.86</v>
+      </c>
+      <c r="F14" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="11" t="n">
-        <v>36.28</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2142.HK</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>和铂医药-B</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="G14" s="10" t="n">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2268.HK</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>药明合联</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>-11.37</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>14.66</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>1519.HK</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>极兔速递-W</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>A·PULLBACK 🟡</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>-10.85</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>9.529999999999999</v>
+      <c r="E15" s="4" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>72.55</v>
       </c>
     </row>
     <row r="16">
@@ -2758,416 +2880,416 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-8.69</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>16.39</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>1519.HK</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>极兔速递-W</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>9.705</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2518.HK</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>汽车之家-S</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>41.84</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>1801.HK</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>信达生物</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>101.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>1579.HK</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>颐海国际</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>-7.83</v>
-      </c>
-      <c r="F17" s="10" t="n">
+      <c r="E20" s="9" t="n">
+        <v>-7.22</v>
+      </c>
+      <c r="F20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="10" t="n">
-        <v>15.07</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>1801.HK</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>信达生物</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="G20" s="9" t="n">
+        <v>15.17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>3347.HK</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>泰格医药</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
-        <v>-7.56</v>
-      </c>
-      <c r="F18" s="4" t="n">
+      <c r="E21" s="4" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>2899.HK</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-6.85</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>35.92</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>0656.HK</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>复星国际</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>5.205</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2319.HK</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>蒙牛乳业</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>18.23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>1179.HK</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>华住集团-S</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>101.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>2319.HK</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>蒙牛乳业</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="G25" s="3" t="n">
+        <v>35.56</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>6160.HK</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>百济神州</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n">
-        <v>-7.21</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>18.02</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2518.HK</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>汽车之家-S</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="E26" s="4" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>215.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2507.HK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>西锐</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>-6.48</v>
-      </c>
-      <c r="F20" s="3" t="n">
+      <c r="E27" s="2" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>42.46</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>1179.HK</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>华住集团-S</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>A·PULLBACK 🟡</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>2899.HK</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>紫金矿业</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>A·PULLBACK 🟡</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>-6.02</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>36.24</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>6160.HK</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>百济神州</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>A·PULLBACK 🟡</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>-5.96</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>214.6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>3347.HK</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>泰格医药</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>A·PULLBACK 🟡</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>-5.94</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>39.3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>0656.HK</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>复星国际</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>A·PULLBACK 🟡</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>5.255</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2507.HK</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>西锐</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>A·PULLBACK 🟡</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>-5.25</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>45.44</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>6055.HK</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>中烟香港</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>A·PULLBACK 🟡</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-4.89</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>24.5</v>
+      <c r="G27" s="2" t="n">
+        <v>45.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>6055.HK</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>中烟香港</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>0027.HK</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>银河娱乐</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>-4.04</v>
-      </c>
-      <c r="F28" s="3" t="n">
+      <c r="E29" s="3" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>33.68</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>0003.HK</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>香港中华煤气</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>A·PULLBACK 🟡</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>-3.56</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>7.115</v>
+      <c r="G29" s="3" t="n">
+        <v>33.7</v>
       </c>
     </row>
     <row r="30">
@@ -3192,236 +3314,238 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>-3.06</v>
+        <v>-3.3</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>0003.HK</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>香港中华煤气</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>A·PULLBACK 🟡</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>0002.HK</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>中电控股</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
-        <v>-2.78</v>
-      </c>
-      <c r="F31" s="12" t="n">
+      <c r="E32" s="11" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="F32" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>76.95</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="G32" s="11" t="n">
+        <v>77.15000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>0883.HK</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>中国海洋石油</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>A·PULLBACK 🟡</t>
         </is>
       </c>
-      <c r="E32" s="9" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="F32" s="9" t="n">
+      <c r="E33" s="8" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="F33" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="9" t="n">
-        <v>24.74</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="G33" s="8" t="n">
+        <v>24.88</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>1109.HK</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>华润置地</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="7" t="n">
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr"/>
+      <c r="F34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="7" t="n">
-        <v>29.6</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="G34" s="12" t="n">
+        <v>29.88</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>0960.HK</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>龙湖集团</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr"/>
+      <c r="F35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>6.015</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>1908.HK</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>建发国际集团</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr"/>
+      <c r="F36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>0688.HK</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>中国海外发展</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="n">
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr"/>
+      <c r="F37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="7" t="n">
-        <v>12.88</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>0960.HK</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>龙湖集团</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>6.13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>1908.HK</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>建发国际集团</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr"/>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>12.19</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>0817.HK</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>中国金茂</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>1.325</v>
+      <c r="G37" s="12" t="n">
+        <v>12.91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>0902.HK</t>
+          <t>0817.HK</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>华能国际电力股份</t>
+          <t>中国金茂</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -3431,79 +3555,79 @@
       </c>
       <c r="E38" s="12" t="inlineStr"/>
       <c r="F38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>2202.HK</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>万科企业</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr"/>
+      <c r="F39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>0902.HK</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>华能国际电力股份</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr"/>
+      <c r="F40" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="12" t="n">
-        <v>5.555</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>9618.HK</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>京东集团-SW</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>108.8</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>0772.HK</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>阅文集团</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>21.44</v>
+      <c r="G40" s="11" t="n">
+        <v>5.66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>9618.HK</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>比亚迪股份</t>
+          <t>京东集团-SW</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3518,166 +3642,166 @@
       </c>
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>108.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>0772.HK</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>阅文集团</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr"/>
+      <c r="F42" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>84.25</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="G42" s="7" t="n">
+        <v>21.48</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>比亚迪股份</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>0175.HK</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>吉利汽车</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="n">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>17.05</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="G44" s="3" t="n">
+        <v>16.79</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>3808.HK</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>中国重汽</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="n">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G43" s="2" t="n">
-        <v>41.88</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="G45" s="2" t="n">
+        <v>42.24</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>2533.HK</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>黑芝麻智能</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="5" t="n">
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="5" t="n">
-        <v>10.82</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>2313.HK</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>申洲国际</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>36.44</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>0921.HK</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>海信家电</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>22.04</v>
+      <c r="G46" s="5" t="n">
+        <v>10.62</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>0780.HK</t>
+          <t>2313.HK</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>同程旅行</t>
+          <t>申洲国际</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3692,253 +3816,253 @@
       </c>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>36.86</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>0921.HK</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>海信家电</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="3" t="n">
-        <v>11.62</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="G48" s="3" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>0780.HK</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>同程旅行</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>11.42</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>0168.HK</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>青岛啤酒股份</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr"/>
-      <c r="F48" s="10" t="n">
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr"/>
+      <c r="F50" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="10" t="n">
-        <v>40.58</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="G50" s="9" t="n">
+        <v>40.94</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>1876.HK</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>百威亚太</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E49" s="10" t="inlineStr"/>
-      <c r="F49" s="10" t="n">
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr"/>
+      <c r="F51" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="10" t="n">
-        <v>5.98</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="G51" s="9" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>2648.HK</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>安井食品</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr"/>
-      <c r="F50" s="10" t="n">
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr"/>
+      <c r="F52" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="10" t="n">
-        <v>63.15</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="G52" s="9" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>3288.HK</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>海天味业</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr"/>
-      <c r="F51" s="10" t="n">
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr"/>
+      <c r="F53" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G51" s="10" t="n">
-        <v>28.14</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="G53" s="9" t="n">
+        <v>28.34</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>9985.HK</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>卫龙美味</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr"/>
-      <c r="F52" s="10" t="n">
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr"/>
+      <c r="F54" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G52" s="10" t="n">
-        <v>7.385</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="G54" s="9" t="n">
+        <v>7.47</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>2367.HK</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>巨子生物</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="10" t="n">
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr"/>
+      <c r="F55" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G53" s="10" t="n">
-        <v>26.1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>2579.HK</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>中伟新材</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>24.86</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2057.HK</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>中通快递-W</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>163.5</v>
+      <c r="G55" s="9" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2618.HK</t>
+          <t>2579.HK</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>京东物流</t>
+          <t>中伟新材</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3956,18 +4080,18 @@
         <v>2</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>11.1</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>6936.HK</t>
+          <t>2057.HK</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>顺丰控股</t>
+          <t>中通快递-W</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3982,21 +4106,21 @@
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>31.02</v>
+        <v>164.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1882.HK</t>
+          <t>2618.HK</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>海天国际</t>
+          <t>京东物流</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4011,79 +4135,79 @@
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>11.14</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>6936.HK</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>顺丰控股</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>1882.HK</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>海天国际</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="2" t="n">
-        <v>18.16</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>6082.HK</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>壁仞科技</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>40.62</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>0763.HK</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>中兴通讯</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>23.56</v>
+      <c r="G60" s="2" t="n">
+        <v>18.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>0981.HK</t>
+          <t>6082.HK</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>壁仞科技</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -4098,21 +4222,21 @@
       </c>
       <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>67.95</v>
+        <v>41.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>0068.HK</t>
+          <t>0763.HK</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>MANYCORE TECH</t>
+          <t>中兴通讯</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -4127,543 +4251,543 @@
       </c>
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>0981.HK</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>0068.HK</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>MANYCORE TECH</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G62" s="5" t="n">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="G64" s="5" t="n">
+        <v>12.47</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>2432.HK</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>越疆</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="n">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="2" t="n">
-        <v>23.4</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="n">
+        <v>23.22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>9880.HK</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>优必选</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="n">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="2" t="n">
-        <v>88.7</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="G66" s="2" t="n">
+        <v>85.55</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>1585.HK</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>雅迪控股</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="n">
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G65" s="3" t="n">
-        <v>8.92</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="G67" s="3" t="n">
+        <v>8.890000000000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>9973.HK</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>奇瑞汽车</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="n">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="G68" s="3" t="n">
         <v>25.2</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>6818.HK</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>中国光大银行</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr"/>
-      <c r="F67" s="6" t="n">
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
+      <c r="F69" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G67" s="6" t="n">
-        <v>2.815</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="G69" s="6" t="n">
+        <v>2.805</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>0659.HK</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>周大福创建</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="n">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G68" s="2" t="n">
-        <v>8.015000000000001</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="G70" s="2" t="n">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>2588.HK</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>中银航空租赁</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="n">
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G69" s="3" t="n">
-        <v>73.59999999999999</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="G71" s="3" t="n">
+        <v>73.15000000000001</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>0552.HK</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>中国通信服务</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="5" t="n">
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G70" s="5" t="n">
-        <v>3.965</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="G72" s="5" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>1186.HK</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>中国铁建</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="n">
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>4.415</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>2128.HK</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>中国联塑</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="n">
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G72" s="2" t="n">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="G74" s="2" t="n">
+        <v>3.445</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>1836.HK</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>九兴控股</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr"/>
-      <c r="F73" s="3" t="n">
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G73" s="3" t="n">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="G75" s="3" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>2150.HK</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>奈雪的茶</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr"/>
-      <c r="F74" s="3" t="n">
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G74" s="3" t="n">
-        <v>0.675</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>0806.HK</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>惠理集团</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr"/>
-      <c r="F75" s="6" t="n">
+      <c r="G76" s="3" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>6608.HK</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>百融云-W</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>1458.HK</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>周黑鸭</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr"/>
+      <c r="F78" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G78" s="9" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2158.HK</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>医渡科技</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="6" t="n">
-        <v>2.045</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>6608.HK</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>百融云-W</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr"/>
-      <c r="F76" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>5.055</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>1458.HK</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>周黑鸭</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr"/>
-      <c r="F77" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" s="10" t="n">
-        <v>1.285</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>2158.HK</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>医渡科技</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>3.91</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="G79" s="4" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>0811.HK</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>新华文轩</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr"/>
-      <c r="F79" s="8" t="n">
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr"/>
+      <c r="F80" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G79" s="8" t="n">
-        <v>7.92</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>3320.HK</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>华润医药</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="4" t="n">
-        <v>4.425</v>
+      <c r="G80" s="7" t="n">
+        <v>7.95</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>0867.HK</t>
+          <t>3320.HK</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>康哲药业</t>
+          <t>华润医药</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -4681,76 +4805,76 @@
         <v>1</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>10.99</v>
+        <v>4.425</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>0867.HK</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>康哲药业</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>10.97</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
         <is>
           <t>0123.HK</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>越秀地产</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C83" s="12" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr"/>
-      <c r="F82" s="7" t="n">
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr"/>
+      <c r="F83" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G82" s="7" t="n">
-        <v>3.265</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>1879.HK</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>曦智科技-P</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr"/>
-      <c r="F83" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>344.8</v>
+      <c r="G83" s="12" t="n">
+        <v>3.26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>2586.HK</t>
+          <t>1879.HK</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>多点数智</t>
+          <t>曦智科技-P</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -4768,18 +4892,18 @@
         <v>1</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>4.21</v>
+        <v>337</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>6682.HK</t>
+          <t>2586.HK</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>范式智能</t>
+          <t>多点数智</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -4794,128 +4918,215 @@
       </c>
       <c r="E85" s="5" t="inlineStr"/>
       <c r="F85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>6682.HK</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>范式智能</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr"/>
+      <c r="F86" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G85" s="5" t="n">
-        <v>29.92</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="G86" s="5" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>6687.HK</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>聚水潭</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr"/>
+      <c r="F87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>9678.HK</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>云知声</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr"/>
+      <c r="F88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>0008.HK</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>电讯盈科</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr"/>
-      <c r="F86" s="8" t="n">
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr"/>
+      <c r="F89" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G86" s="8" t="n">
-        <v>5.285</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="G89" s="7" t="n">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>0576.HK</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>浙江沪杭甬</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="n">
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G87" s="2" t="n">
-        <v>6.085</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="12" t="inlineStr">
+      <c r="G90" s="2" t="n">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
         <is>
           <t>1071.HK</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>华电国际电力股份</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C91" s="11" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>B·EXIT 🔴</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr"/>
-      <c r="F88" s="12" t="n">
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>B·EXIT 🔴</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr"/>
+      <c r="F91" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G88" s="12" t="n">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
+      <c r="G91" s="11" t="n">
+        <v>3.985</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>2689.HK</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>玖龙纸业</t>
         </is>
       </c>
-      <c r="C89" s="11" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D89" s="11" t="inlineStr">
+      <c r="D92" s="10" t="inlineStr">
         <is>
           <t>C·PULLBACK 🟠</t>
         </is>
       </c>
-      <c r="E89" s="11" t="n">
-        <v>-22.66</v>
-      </c>
-      <c r="F89" s="11" t="n">
+      <c r="E92" s="10" t="n">
+        <v>-22.18</v>
+      </c>
+      <c r="F92" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="G89" s="11" t="n">
-        <v>6.485</v>
+      <c r="G92" s="10" t="n">
+        <v>6.525</v>
       </c>
     </row>
   </sheetData>

--- a/data/v5_4_hk.xlsx
+++ b/data/v5_4_hk.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -985,366 +985,366 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>0285.HK</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>比亚迪电子</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>3993.HK</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>洛阳钼业</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>工业金属</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>SOS-B</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>16.943</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>0136.HK</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>中国儒意</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>媒体及娱乐</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>SOS-B</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>1.372</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>-6.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>1138.HK</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>中远海能</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>交运</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>SOS-B</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>16.852</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>9699.HK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>顺丰同城</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>交运</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>SOS-C</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>8.426</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>-3.97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>0999.HK</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>小菜园</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>旅游及消闲设施</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>SOS-C</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>7.659</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>6078.HK</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>海吉亚医疗</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>其他医疗保健</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>SETUP_OK</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>SOS-C</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>10.275</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>0354.HK</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>中国软件国际</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>软件服务</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>SOS-B</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>25.52</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>25.342</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>-4.13</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>3993.HK</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>洛阳钼业</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>工业金属</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>SOS-C</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>3.815</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>3.883</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>-4.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>2799.HK</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>中信金融资产</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>其他金融</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>SOS-B</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>17.61</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>16.943</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>0136.HK</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>中国儒意</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>媒体及娱乐</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>SETUP_OK</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>SOS-B</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>1.372</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>-6.61</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>1138.HK</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>中远海能</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>交运</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>SETUP_OK</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>SOS-B</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>16.852</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>9699.HK</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>顺丰同城</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>交运</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>SETUP_OK</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>8.426</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>-3.97</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>0999.HK</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>小菜园</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>旅游及消闲设施</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>SETUP_OK</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>SOS-C</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>7.659</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>6078.HK</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>海吉亚医疗</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>其他医疗保健</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>SETUP_OK</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>SOS-C</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>10.275</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>-2.78</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>0354.HK</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>中国软件国际</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>软件服务</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>SETUP_OK</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>SOS-C</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>3.815</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>3.883</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>-4.75</v>
+      <c r="G18" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>-5.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2799.HK</t>
+          <t>3958.HK</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>中信金融资产</t>
+          <t>东方证券</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1368,235 +1368,191 @@
         </is>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.655</v>
+        <v>5.8</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.646</v>
+        <v>5.855</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>7.58</v>
+        <v>4.84</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-5.08</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>3958.HK</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>东方证券</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>其他金融</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>1797.HK</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>东方甄选</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G20" s="9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>5.855</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>-2.31</v>
+      <c r="G20" s="10" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>25.544</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0.47</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>1797.HK</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>东方甄选</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>1357.HK</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>美图公司</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>媒体及娱乐</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G21" s="10" t="n">
-        <v>26.62</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>25.544</v>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>0.47</v>
+      <c r="G21" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>4.649</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>-6.61</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>1357.HK</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>美图公司</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>媒体及娱乐</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>2688.HK</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>新奥能源</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>公共事业</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>4.649</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>-6.61</v>
+      <c r="G22" s="11" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>2688.HK</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>新奥能源</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>公共事业</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>3668.HK</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>兖煤澳大利亚</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>能源</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>SETUP_OK</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>SOS-C</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="H23" s="11" t="n">
-        <v>49.29</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>3668.HK</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>兖煤澳大利亚</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>能源</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>SETUP_OK</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>SOS-C</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="n">
+      <c r="G23" s="8" t="n">
         <v>36.22</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="H23" s="8" t="n">
         <v>34.253</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I23" s="8" t="n">
         <v>6.88</v>
       </c>
-      <c r="J24" s="8" t="n">
+      <c r="J23" s="8" t="n">
         <v>1.73</v>
       </c>
     </row>
@@ -3089,12 +3045,12 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>0688.HK</t>
+          <t>0960.HK</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>中国海外发展</t>
+          <t>龙湖集团</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -3112,18 +3068,18 @@
         <v>2</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>13.01</v>
+        <v>6.225</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>0960.HK</t>
+          <t>1908.HK</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>龙湖集团</t>
+          <t>建发国际集团</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -3141,18 +3097,18 @@
         <v>2</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>6.225</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>1908.HK</t>
+          <t>0688.HK</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>建发国际集团</t>
+          <t>中国海外发展</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -3170,7 +3126,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>12.7</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="31">
@@ -3408,12 +3364,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>0168.HK</t>
+          <t>1876.HK</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>青岛啤酒股份</t>
+          <t>百威亚太</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -3431,18 +3387,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>41.46</v>
+        <v>6.115</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>1876.HK</t>
+          <t>0168.HK</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>百威亚太</t>
+          <t>青岛啤酒股份</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -3460,7 +3416,7 @@
         <v>2</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>6.115</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="41">
@@ -4630,7 +4586,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>扫描日期：2026-09-08</t>
+          <t>扫描日期：2026-09-09</t>
         </is>
       </c>
     </row>
